--- a/nmoreau/ig/all-profiles.xlsx
+++ b/nmoreau/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T12:12:45+00:00</t>
+    <t>2025-04-24T12:14:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/all-profiles.xlsx
+++ b/nmoreau/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T12:14:49+00:00</t>
+    <t>2025-04-24T12:53:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/all-profiles.xlsx
+++ b/nmoreau/ig/all-profiles.xlsx
@@ -30,7 +30,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.fr/fhir/fr/preadmission/StructureDefinition/appointment-context-extension</t>
+    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/appointment-context-extension</t>
   </si>
   <si>
     <t>Version</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-25T09:56:34+00:00</t>
+    <t>2025-04-25T14:29:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -331,7 +331,7 @@
     <t>Extension.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.fr/fhir/fr/preadmission/StructureDefinition/preadmission-consent-fr)
+    <t xml:space="preserve">Reference(https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/preadmission-consent-fr)
 </t>
   </si>
   <si>
@@ -348,7 +348,7 @@
     <t>appointment-questionnaire-response</t>
   </si>
   <si>
-    <t>http://hl7.fr/fhir/fr/preadmission/StructureDefinition/appointment-questionnaire-response</t>
+    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/appointment-questionnaire-response</t>
   </si>
   <si>
     <t>PreadmissionAppointmentQuestionnaireResponseFr</t>
@@ -367,7 +367,7 @@
     <t>encounter-agent-instructions</t>
   </si>
   <si>
-    <t>http://hl7.fr/fhir/fr/preadmission/StructureDefinition/encounter-agent-instructions</t>
+    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/encounter-agent-instructions</t>
   </si>
   <si>
     <t>EncounterAgentInstructions</t>
@@ -385,7 +385,7 @@
     <t>encounter-patient-comment</t>
   </si>
   <si>
-    <t>http://hl7.fr/fhir/fr/preadmission/StructureDefinition/encounter-patient-comment</t>
+    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/encounter-patient-comment</t>
   </si>
   <si>
     <t>EncounterPatientComment</t>
@@ -400,7 +400,7 @@
     <t>fr-coverage-amc-extended</t>
   </si>
   <si>
-    <t>http://hl7.fr/fhir/fr/preadmission/StructureDefinition/fr-coverage-amc-extended</t>
+    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/fr-coverage-amc-extended</t>
   </si>
   <si>
     <t>FrCoverageAMCExtension</t>
@@ -527,7 +527,7 @@
     <t>hl7.fhir.fr.preadmission.statut-preadmission</t>
   </si>
   <si>
-    <t>http://hl7.fr/fhir/fr/preadmission/StructureDefinition/hl7.fhir.fr.preadmission.statut-preadmission</t>
+    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/hl7.fhir.fr.preadmission.statut-preadmission</t>
   </si>
   <si>
     <t>PreadmissionStatutFr</t>
@@ -749,7 +749,7 @@
     <t>preadmission-appointment-fr</t>
   </si>
   <si>
-    <t>http://hl7.fr/fhir/fr/preadmission/StructureDefinition/preadmission-appointment-fr</t>
+    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/preadmission-appointment-fr</t>
   </si>
   <si>
     <t>PreadmissionAppointmentFr</t>
@@ -1064,7 +1064,7 @@
     <t>questionnaire</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.fr/fhir/fr/preadmission/StructureDefinition/appointment-questionnaire-response}
+    <t xml:space="preserve">Extension {https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/appointment-questionnaire-response}
 </t>
   </si>
   <si>
@@ -1074,7 +1074,7 @@
     <t>consentements</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.fr/fhir/fr/preadmission/StructureDefinition/preadmission-consent-fr-exntension}
+    <t xml:space="preserve">Extension {https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/preadmission-consent-fr-exntension}
 </t>
   </si>
   <si>
@@ -1497,7 +1497,7 @@
     <t>preadmission-consent-fr-exntension</t>
   </si>
   <si>
-    <t>http://hl7.fr/fhir/fr/preadmission/StructureDefinition/preadmission-consent-fr-exntension</t>
+    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/preadmission-consent-fr-exntension</t>
   </si>
   <si>
     <t>PreadmissionConsentementsExtension</t>
@@ -1506,7 +1506,7 @@
     <t>preadmission-consent-fr</t>
   </si>
   <si>
-    <t>http://hl7.fr/fhir/fr/preadmission/StructureDefinition/preadmission-consent-fr</t>
+    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/preadmission-consent-fr</t>
   </si>
   <si>
     <t>PreadmissionConsentFr</t>
@@ -1627,7 +1627,7 @@
     <t>A classification of the type of consents found in the statement. This element supports indexing and retrieval of consent statements.</t>
   </si>
   <si>
-    <t>http://hl7.fr/fhir/fr/preadmission/ValueSet/consent-category-value-set</t>
+    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/ValueSet/consent-category-value-set</t>
   </si>
   <si>
     <t>Consent.patient</t>
@@ -2005,7 +2005,7 @@
     <t>alimentationDmp</t>
   </si>
   <si>
-    <t>http://hl7.fr/fhir/fr/preadmission/ValueSet/dmp-feed-consent-status-vs</t>
+    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/ValueSet/dmp-feed-consent-status-vs</t>
   </si>
   <si>
     <t>Consent.provision.code:consultationDmp</t>
@@ -2014,7 +2014,7 @@
     <t>consultationDmp</t>
   </si>
   <si>
-    <t>http://hl7.fr/fhir/fr/preadmission/ValueSet/dmp-access-consent-status-vs</t>
+    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/ValueSet/dmp-access-consent-status-vs</t>
   </si>
   <si>
     <t>Consent.provision.dataPeriod</t>
@@ -2086,7 +2086,7 @@
     <t>preadmission-coverage-fr</t>
   </si>
   <si>
-    <t>http://hl7.fr/fhir/fr/preadmission/StructureDefinition/preadmission-coverage-fr</t>
+    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/preadmission-coverage-fr</t>
   </si>
   <si>
     <t>PreadmissionCoverageFr</t>
@@ -2144,7 +2144,7 @@
     <t>informationsAmc</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.fr/fhir/fr/preadmission/StructureDefinition/fr-coverage-amc-extended}
+    <t xml:space="preserve">Extension {https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/fr-coverage-amc-extended}
 </t>
   </si>
   <si>
@@ -2235,7 +2235,7 @@
     <t>Coverage.type.coding.code</t>
   </si>
   <si>
-    <t>http://hl7.fr/fhir/fr/preadmission/ValueSet/type-couverture-sociale-vs</t>
+    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/ValueSet/type-couverture-sociale-vs</t>
   </si>
   <si>
     <t>Coverage.type.coding.display</t>
@@ -2695,7 +2695,7 @@
     <t>preadmission-documentreference-fr</t>
   </si>
   <si>
-    <t>http://hl7.fr/fhir/fr/preadmission/StructureDefinition/preadmission-documentreference-fr</t>
+    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/preadmission-documentreference-fr</t>
   </si>
   <si>
     <t>PreadmissionDocumentReferenceFr</t>
@@ -3356,7 +3356,7 @@
     <t>preadmission-encounter-fr</t>
   </si>
   <si>
-    <t>http://hl7.fr/fhir/fr/preadmission/StructureDefinition/preadmission-encounter-fr</t>
+    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/preadmission-encounter-fr</t>
   </si>
   <si>
     <t>PreadmissionEncounterFr</t>
@@ -3454,7 +3454,7 @@
     <t>remarquePatient</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.fr/fhir/fr/preadmission/StructureDefinition/encounter-patient-comment}
+    <t xml:space="preserve">Extension {https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/encounter-patient-comment}
 </t>
   </si>
   <si>
@@ -3464,7 +3464,7 @@
     <t>consignesAgent</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.fr/fhir/fr/preadmission/StructureDefinition/encounter-agent-instructions}
+    <t xml:space="preserve">Extension {https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/encounter-agent-instructions}
 </t>
   </si>
   <si>
@@ -3474,7 +3474,7 @@
     <t>preadmissionStatus</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.fr/fhir/fr/preadmission/StructureDefinition/hl7.fhir.fr.preadmission.statut-preadmission}
+    <t xml:space="preserve">Extension {https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/hl7.fhir.fr.preadmission.statut-preadmission}
 </t>
   </si>
   <si>
@@ -3738,7 +3738,7 @@
     <t>Encounter.class.code</t>
   </si>
   <si>
-    <t>http://hl7.fr/fhir/fr/preadmission/ValueSet/type-venue-encounter-vs</t>
+    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/ValueSet/type-venue-encounter-vs</t>
   </si>
   <si>
     <t>Encounter.class.display</t>
@@ -3912,7 +3912,7 @@
     <t>Encounter.appointment</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.fr/fhir/fr/preadmission/StructureDefinition/preadmission-appointment-fr)
+    <t xml:space="preserve">Reference(https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/preadmission-appointment-fr)
 </t>
   </si>
   <si>
@@ -6603,7 +6603,7 @@
     <col min="24" max="24" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="124.2265625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="61.234375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="77.546875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/nmoreau/ig/all-profiles.xlsx
+++ b/nmoreau/ig/all-profiles.xlsx
@@ -30,7 +30,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/appointment-context-extension</t>
+    <t>http://hl7.fr/fhir/fr/preadmission/StructureDefinition/appointment-context-extension</t>
   </si>
   <si>
     <t>Version</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-25T16:50:14+00:00</t>
+    <t>2025-04-28T06:55:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -331,7 +331,7 @@
     <t>Extension.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/preadmission-consent-fr)
+    <t xml:space="preserve">Reference(http://hl7.fr/fhir/fr/preadmission/StructureDefinition/preadmission-consent-fr)
 </t>
   </si>
   <si>
@@ -348,7 +348,7 @@
     <t>appointment-questionnaire-response</t>
   </si>
   <si>
-    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/appointment-questionnaire-response</t>
+    <t>http://hl7.fr/fhir/fr/preadmission/StructureDefinition/appointment-questionnaire-response</t>
   </si>
   <si>
     <t>PreadmissionAppointmentQuestionnaireResponseFr</t>
@@ -367,7 +367,7 @@
     <t>encounter-agent-instructions</t>
   </si>
   <si>
-    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/encounter-agent-instructions</t>
+    <t>http://hl7.fr/fhir/fr/preadmission/StructureDefinition/encounter-agent-instructions</t>
   </si>
   <si>
     <t>EncounterAgentInstructions</t>
@@ -385,7 +385,7 @@
     <t>encounter-patient-comment</t>
   </si>
   <si>
-    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/encounter-patient-comment</t>
+    <t>http://hl7.fr/fhir/fr/preadmission/StructureDefinition/encounter-patient-comment</t>
   </si>
   <si>
     <t>EncounterPatientComment</t>
@@ -400,7 +400,7 @@
     <t>fr-coverage-amc-extended</t>
   </si>
   <si>
-    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/fr-coverage-amc-extended</t>
+    <t>http://hl7.fr/fhir/fr/preadmission/StructureDefinition/fr-coverage-amc-extended</t>
   </si>
   <si>
     <t>FrCoverageAMCExtension</t>
@@ -527,7 +527,7 @@
     <t>hl7.fhir.fr.preadmission.statut-preadmission</t>
   </si>
   <si>
-    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/hl7.fhir.fr.preadmission.statut-preadmission</t>
+    <t>http://hl7.fr/fhir/fr/preadmission/StructureDefinition/hl7.fhir.fr.preadmission.statut-preadmission</t>
   </si>
   <si>
     <t>PreadmissionStatutFr</t>
@@ -749,7 +749,7 @@
     <t>preadmission-appointment-fr</t>
   </si>
   <si>
-    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/preadmission-appointment-fr</t>
+    <t>http://hl7.fr/fhir/fr/preadmission/StructureDefinition/preadmission-appointment-fr</t>
   </si>
   <si>
     <t>PreadmissionAppointmentFr</t>
@@ -1064,7 +1064,7 @@
     <t>questionnaire</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/appointment-questionnaire-response}
+    <t xml:space="preserve">Extension {http://hl7.fr/fhir/fr/preadmission/StructureDefinition/appointment-questionnaire-response}
 </t>
   </si>
   <si>
@@ -1074,7 +1074,7 @@
     <t>consentements</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/preadmission-consent-fr-exntension}
+    <t xml:space="preserve">Extension {http://hl7.fr/fhir/fr/preadmission/StructureDefinition/preadmission-consent-fr-exntension}
 </t>
   </si>
   <si>
@@ -1497,7 +1497,7 @@
     <t>preadmission-consent-fr-exntension</t>
   </si>
   <si>
-    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/preadmission-consent-fr-exntension</t>
+    <t>http://hl7.fr/fhir/fr/preadmission/StructureDefinition/preadmission-consent-fr-exntension</t>
   </si>
   <si>
     <t>PreadmissionConsentementsExtension</t>
@@ -1506,7 +1506,7 @@
     <t>preadmission-consent-fr</t>
   </si>
   <si>
-    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/preadmission-consent-fr</t>
+    <t>http://hl7.fr/fhir/fr/preadmission/StructureDefinition/preadmission-consent-fr</t>
   </si>
   <si>
     <t>PreadmissionConsentFr</t>
@@ -1627,7 +1627,7 @@
     <t>A classification of the type of consents found in the statement. This element supports indexing and retrieval of consent statements.</t>
   </si>
   <si>
-    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/ValueSet/consent-category-value-set</t>
+    <t>http://hl7.fr/fhir/fr/preadmission/ValueSet/consent-category-value-set</t>
   </si>
   <si>
     <t>Consent.patient</t>
@@ -2009,7 +2009,7 @@
     <t>alimentationDmp</t>
   </si>
   <si>
-    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/ValueSet/dmp-feed-consent-status-vs</t>
+    <t>http://hl7.fr/fhir/fr/preadmission/ValueSet/dmp-feed-consent-status-vs</t>
   </si>
   <si>
     <t>Consent.provision.code:consultationDmp</t>
@@ -2018,7 +2018,7 @@
     <t>consultationDmp</t>
   </si>
   <si>
-    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/ValueSet/dmp-access-consent-status-vs</t>
+    <t>http://hl7.fr/fhir/fr/preadmission/ValueSet/dmp-access-consent-status-vs</t>
   </si>
   <si>
     <t>Consent.provision.dataPeriod</t>
@@ -2090,7 +2090,7 @@
     <t>preadmission-coverage-fr</t>
   </si>
   <si>
-    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/preadmission-coverage-fr</t>
+    <t>http://hl7.fr/fhir/fr/preadmission/StructureDefinition/preadmission-coverage-fr</t>
   </si>
   <si>
     <t>PreadmissionCoverageFr</t>
@@ -2148,7 +2148,7 @@
     <t>informationsAmc</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/fr-coverage-amc-extended}
+    <t xml:space="preserve">Extension {http://hl7.fr/fhir/fr/preadmission/StructureDefinition/fr-coverage-amc-extended}
 </t>
   </si>
   <si>
@@ -2239,7 +2239,7 @@
     <t>Coverage.type.coding.code</t>
   </si>
   <si>
-    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/ValueSet/type-couverture-sociale-vs</t>
+    <t>http://hl7.fr/fhir/fr/preadmission/ValueSet/type-couverture-sociale-vs</t>
   </si>
   <si>
     <t>Coverage.type.coding.display</t>
@@ -2699,7 +2699,7 @@
     <t>preadmission-documentreference-fr</t>
   </si>
   <si>
-    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/preadmission-documentreference-fr</t>
+    <t>http://hl7.fr/fhir/fr/preadmission/StructureDefinition/preadmission-documentreference-fr</t>
   </si>
   <si>
     <t>PreadmissionDocumentReferenceFr</t>
@@ -3360,7 +3360,7 @@
     <t>preadmission-encounter-fr</t>
   </si>
   <si>
-    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/preadmission-encounter-fr</t>
+    <t>http://hl7.fr/fhir/fr/preadmission/StructureDefinition/preadmission-encounter-fr</t>
   </si>
   <si>
     <t>PreadmissionEncounterFr</t>
@@ -3458,7 +3458,7 @@
     <t>remarquePatient</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/encounter-patient-comment}
+    <t xml:space="preserve">Extension {http://hl7.fr/fhir/fr/preadmission/StructureDefinition/encounter-patient-comment}
 </t>
   </si>
   <si>
@@ -3468,7 +3468,7 @@
     <t>consignesAgent</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/encounter-agent-instructions}
+    <t xml:space="preserve">Extension {http://hl7.fr/fhir/fr/preadmission/StructureDefinition/encounter-agent-instructions}
 </t>
   </si>
   <si>
@@ -3478,7 +3478,7 @@
     <t>preadmissionStatus</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/hl7.fhir.fr.preadmission.statut-preadmission}
+    <t xml:space="preserve">Extension {http://hl7.fr/fhir/fr/preadmission/StructureDefinition/hl7.fhir.fr.preadmission.statut-preadmission}
 </t>
   </si>
   <si>
@@ -3742,7 +3742,7 @@
     <t>Encounter.class.code</t>
   </si>
   <si>
-    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/ValueSet/type-venue-encounter-vs</t>
+    <t>http://hl7.fr/fhir/fr/preadmission/ValueSet/type-venue-encounter-vs</t>
   </si>
   <si>
     <t>Encounter.class.display</t>
@@ -3916,7 +3916,7 @@
     <t>Encounter.appointment</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/preadmission-appointment-fr)
+    <t xml:space="preserve">Reference(http://hl7.fr/fhir/fr/preadmission/StructureDefinition/preadmission-appointment-fr)
 </t>
   </si>
   <si>
@@ -6607,7 +6607,7 @@
     <col min="24" max="24" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="124.2265625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="77.546875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="61.234375" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/nmoreau/ig/all-profiles.xlsx
+++ b/nmoreau/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T06:55:35+00:00</t>
+    <t>2025-04-28T10:41:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/all-profiles.xlsx
+++ b/nmoreau/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-05T08:51:40+00:00</t>
+    <t>2025-05-06T13:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/all-profiles.xlsx
+++ b/nmoreau/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-26T06:59:47+00:00</t>
+    <t>2025-06-02T15:02:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/all-profiles.xlsx
+++ b/nmoreau/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-28T10:00:18+00:00</t>
+    <t>2025-11-19T09:47:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/all-profiles.xlsx
+++ b/nmoreau/ig/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-19T09:47:12+00:00</t>
+    <t>2026-01-14T12:51:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
